--- a/seo/media360-seo-keyword-map.xlsx
+++ b/seo/media360-seo-keyword-map.xlsx
@@ -1051,7 +1051,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Contact Media 360 Concept at HiLITE Business Park, Calicut: WhatsApp or call +91 9061 460 360, email us, or send your project details.</t>
+          <t>Contact Media 360 Concept at HiLITE Business Park, Calicut: WhatsApp or call +91 81578 74951, email us, or send your project details.</t>
         </is>
       </c>
       <c r="I5" s="6" t="n">
